--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,17 +250,17 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgcReadme.editeurSortant</t>
+    <t>pdlgcReadme.systemeEmetteur</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgcFournisseurSortant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgcSystem
 </t>
   </si>
   <si>
-    <t>Editeur responsable de l'export des données LGC et application utilisée</t>
+    <t>Système responsable de l'export des données LGC et informations de l'éditeur émetteur</t>
   </si>
   <si>
     <t>pdlgcReadme.instructions</t>
@@ -581,8 +581,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.6328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.6328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.1875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.1875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -591,7 +591,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.18359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -612,7 +612,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="23.6328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="26.1875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,17 +250,17 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgcReadme.systemeEmetteur</t>
+    <t>pdlgcReadme.author</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgcSystem
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgcAuthor
 </t>
   </si>
   <si>
-    <t>Système responsable de l'export des données LGC et informations de l'éditeur émetteur</t>
+    <t>auteur responsable de l'export des données LGC et informations de l'éditeur émetteur</t>
   </si>
   <si>
     <t>pdlgcReadme.instructions</t>
@@ -581,8 +581,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="26.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.8671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.8671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -591,7 +591,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.18359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -612,7 +612,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="26.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="22.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
